--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A4C441-B459-446C-956F-5F1EAD1F7E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAC4336-F79D-43F3-8B80-55D1F0AC444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1995" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -105,10 +94,6 @@
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>night</t>
   </si>
   <si>
@@ -221,17 +206,21 @@
   <si>
     <t>hei</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>night_end</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -245,7 +234,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -266,7 +255,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -414,7 +403,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -693,27 +682,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -730,31 +719,31 @@
         <v>18</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="J1" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="O1" s="15" t="s">
         <v>17</v>
@@ -763,28 +752,28 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>31</v>
-      </c>
       <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -799,65 +788,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -869,20 +858,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -908,7 +897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -921,10 +910,10 @@
       <c r="F2" s="7"/>
       <c r="G2" s="2"/>
       <c r="H2" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -932,7 +921,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -941,10 +930,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -952,7 +941,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -961,10 +950,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -972,7 +961,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -981,10 +970,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -997,10 +986,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1008,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -1017,10 +1006,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1028,7 +1017,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1037,10 +1026,10 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1048,19 +1037,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1068,19 +1057,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1088,21 +1077,21 @@
         <v>7</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1114,7 +1103,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAC4336-F79D-43F3-8B80-55D1F0AC444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29025E64-374D-49A9-B3E8-0EA99C2C250F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1995" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
   <si>
     <t>StoryID</t>
   </si>
@@ -210,17 +221,240 @@
   <si>
     <t>night_end</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>current_scene</t>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20_01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20_02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20_03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一行人来到王府</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>启禀王爷，人都带来了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>这几位是朝廷派来查赈灾药材案的钦差。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>锦衣卫</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>你就是李东璧？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>正是草民。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧将前前后后发生的事情一五一十告予钦差</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +468,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -255,7 +489,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -342,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -401,9 +635,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -682,27 +919,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -752,7 +989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
         <v>29</v>
       </c>
@@ -788,65 +1025,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -857,21 +1094,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -897,7 +1134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -908,12 +1145,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="H2" s="19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -933,7 +1172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -948,12 +1187,14 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="H4" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -968,12 +1209,14 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="H5" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -984,12 +1227,14 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="H6" s="19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1009,7 +1254,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1023,13 +1268,15 @@
         <v>10</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="22" t="s">
+        <v>58</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1043,13 +1290,17 @@
         <v>41</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1069,7 +1320,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1085,33 +1336,175 @@
       <c r="E11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="22" t="s">
+        <v>58</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="20" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29025E64-374D-49A9-B3E8-0EA99C2C250F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD077783-EFA6-4479-BBD2-B2A7AA1A1FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,19 +430,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>锦衣卫</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>你就是李东璧？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>正是草民。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李东璧将前前后后发生的事情一五一十告予钦差</t>
+    <t>李东璧将前前后后发生的事情一五一十地禀明钦差</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陆丁</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>在下北镇抚司陆丁，你就是李东璧？</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1439,7 +1439,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1455,13 +1455,11 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
+      <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
       <c r="D18" s="2"/>
@@ -1471,9 +1469,7 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
+      <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
       <c r="D19" s="2"/>
@@ -1483,9 +1479,7 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
+      <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
       <c r="D20" s="2"/>
@@ -1495,9 +1489,7 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
+      <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
       <c r="D21" s="2"/>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD077783-EFA6-4479-BBD2-B2A7AA1A1FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AB2389-6143-4923-AB04-1991FA8320B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -442,7 +442,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>在下北镇抚司陆丁，你就是李东璧？</t>
+    <t>北镇抚司陆丁，你就是李东璧？</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AB2389-6143-4923-AB04-1991FA8320B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64837E55-0673-4079-AAFF-1715BD0A6327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,10 +195,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>贤弟，你没事吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>王府护卫</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -443,6 +439,10 @@
   </si>
   <si>
     <t>北镇抚司陆丁，你就是李东璧？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>贤弟，你没事吧。王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -997,7 +997,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
@@ -1146,7 +1146,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>33</v>
@@ -1188,7 +1188,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H4" s="19" t="s">
         <v>37</v>
@@ -1210,7 +1210,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" s="19" t="s">
         <v>38</v>
@@ -1228,7 +1228,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H6" s="19" t="s">
         <v>39</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="19" t="s">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1308,16 +1308,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1334,14 +1334,14 @@
         <v>9</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1356,10 +1356,10 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1370,7 +1370,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1379,7 +1379,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1390,7 +1390,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>41</v>
@@ -1399,7 +1399,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1439,7 +1439,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1455,7 +1455,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64837E55-0673-4079-AAFF-1715BD0A6327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA99BEA0-D6C9-4D2F-8E06-696B269F16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
   <si>
     <t>LineIndex</t>
   </si>
@@ -83,62 +69,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>night</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>020</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -213,10 +152,6 @@
   <si>
     <t>hei</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>night_end</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>current_scene</t>
@@ -444,17 +379,105 @@
   <si>
     <t>贤弟，你没事吧。王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>night_end</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -468,7 +491,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -489,20 +512,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -516,8 +531,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,20 +569,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -576,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -599,48 +638,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -918,176 +977,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="25" customFormat="1">
+      <c r="A1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="25" customFormat="1">
+      <c r="A2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="27">
+        <v>1</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="M2" s="26"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="L3" s="17"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="13"/>
+      <c r="T2" s="28"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="12"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="8:8" ht="18.75">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="8:8" ht="18.75">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="8:8" ht="18.75">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{5D882534-A962-491C-9801-D3034B8FBE40}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{E1354158-B626-4529-B30B-7D91853B7494}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{106EFE27-7972-43CB-8881-4291FA24AC23}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{C91A2686-CBDE-4E8A-B80F-313893E6C91D}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{E7BE2FF6-A40A-4141-BBC5-9728C7A985D6}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1095,370 +1182,370 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="19"/>
+        <v>5</v>
+      </c>
+      <c r="C2" s="14"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>36</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>36</v>
+        <v>6</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="22" t="s">
-        <v>57</v>
+      <c r="F8" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="22" t="s">
-        <v>57</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>57</v>
+        <v>8</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H11" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>43</v>
+        <v>6</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>27</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H14" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>61</v>
+        <v>6</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H15" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H16" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H17" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -1468,7 +1555,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -1478,7 +1565,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
@@ -1488,7 +1575,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA99BEA0-D6C9-4D2F-8E06-696B269F16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7EFA65-E5C7-4587-BC85-D1ADC57E4F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19050" yWindow="6090" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>LineIndex</t>
   </si>
@@ -468,6 +479,10 @@
   <si>
     <t>night_end</t>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
@@ -477,7 +492,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -491,7 +506,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -512,7 +527,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -615,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -697,9 +712,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -978,26 +996,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="25" customFormat="1">
+    <row r="1" spans="1:20" s="25" customFormat="1" ht="18">
       <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
@@ -1059,7 +1077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="25" customFormat="1">
+    <row r="2" spans="1:20" s="25" customFormat="1" ht="18">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -1101,56 +1119,56 @@
       <c r="L3" s="12"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:20" ht="18.75">
+    <row r="4" spans="1:20">
       <c r="C4" s="8"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:20" ht="18.75">
+    <row r="5" spans="1:20">
       <c r="C5" s="8"/>
       <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:20" ht="18.75">
+    <row r="6" spans="1:20">
       <c r="C6" s="8"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:20" ht="18.75">
+    <row r="7" spans="1:20">
       <c r="C7" s="8"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:20" ht="18.75">
+    <row r="8" spans="1:20">
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:20" ht="18.75">
+    <row r="9" spans="1:20">
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:20" ht="18.75">
+    <row r="10" spans="1:20">
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:20" ht="18.75">
+    <row r="11" spans="1:20">
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:20" ht="18.75">
+    <row r="12" spans="1:20">
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:20" ht="18.75">
+    <row r="13" spans="1:20">
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:20" ht="18.75">
+    <row r="14" spans="1:20">
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:20" ht="18.75">
+    <row r="15" spans="1:20">
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:20" ht="18.75">
+    <row r="16" spans="1:20">
       <c r="H16" s="10"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="8:8">
@@ -1181,21 +1199,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1220,8 +1238,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1238,8 +1259,9 @@
       <c r="H2" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1258,8 +1280,9 @@
       <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1280,8 +1303,9 @@
       <c r="H4" s="14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1302,8 +1326,9 @@
       <c r="H5" s="14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1320,8 +1345,9 @@
       <c r="H6" s="14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1340,8 +1366,9 @@
       <c r="H7" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1362,8 +1389,9 @@
       <c r="H8" s="14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1386,8 +1414,9 @@
       <c r="H9" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1406,8 +1435,9 @@
       <c r="H10" s="15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1430,8 +1460,9 @@
       <c r="H11" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1448,8 +1479,9 @@
       <c r="H12" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1468,8 +1500,9 @@
       <c r="H13" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1488,8 +1521,9 @@
       <c r="H14" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1508,8 +1542,9 @@
       <c r="H15" s="17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1528,8 +1563,9 @@
       <c r="H16" s="17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1544,8 +1580,9 @@
       <c r="H17" s="17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -1554,8 +1591,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -1564,8 +1602,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
@@ -1574,8 +1613,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
@@ -1584,6 +1624,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7EFA65-E5C7-4587-BC85-D1ADC57E4F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31485291-5589-4738-9020-A2F338827601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19050" yWindow="6090" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -388,10 +388,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>贤弟，你没事吧。王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>剧情ID</t>
     <phoneticPr fontId="9"/>
   </si>
@@ -482,6 +478,10 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>贤弟，你没事吧？王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1017,58 +1017,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="25" customFormat="1" ht="18">
       <c r="A1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="J1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="L1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="N1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="O1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="P1" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="Q1" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>65</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>66</v>
       </c>
       <c r="S1" s="24" t="s">
         <v>12</v>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="27">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1412,7 +1412,7 @@
         <v>34</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I9" s="3"/>
     </row>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31485291-5589-4738-9020-A2F338827601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774A70A5-AF44-4BD6-AD0A-582E759180BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -246,52 +235,6 @@
         <charset val="134"/>
       </rPr>
       <t>20_02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20</t>
     </r>
     <r>
       <rPr>
@@ -483,6 +426,52 @@
     <t>贤弟，你没事吧？王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20_04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -492,7 +481,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -506,7 +495,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -527,7 +516,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -717,7 +706,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -996,79 +985,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="25" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="25" customFormat="1">
       <c r="A1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="J1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="L1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="N1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="O1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="P1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="Q1" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>64</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>65</v>
       </c>
       <c r="S1" s="24" t="s">
         <v>12</v>
@@ -1077,7 +1066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="25" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="25" customFormat="1">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -1085,7 +1074,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" s="27">
         <v>1</v>
@@ -1202,14 +1191,14 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="92.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.3984375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="92.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1239,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1340,7 +1329,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>25</v>
@@ -1383,7 +1372,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="14" t="s">
@@ -1406,13 +1395,13 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -1454,7 +1443,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="15" t="s">
@@ -1474,10 +1463,10 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -1498,7 +1487,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" s="3"/>
     </row>
@@ -1510,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>27</v>
@@ -1519,7 +1508,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I14" s="3"/>
     </row>
@@ -1531,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>9</v>
@@ -1540,7 +1529,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" s="3"/>
     </row>
@@ -1561,7 +1550,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16" s="3"/>
     </row>
@@ -1578,7 +1567,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" s="3"/>
     </row>

--- a/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
+++ b/DataTables/DetailText/剧情/020夜晚遇刺.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774A70A5-AF44-4BD6-AD0A-582E759180BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA37F951-3056-4585-9ED3-6B90888B66C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
   <si>
     <t>LineIndex</t>
   </si>
@@ -470,6 +470,10 @@
       </rPr>
       <t>.png</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Music/020/圍剿夜襲.mp3</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1248,7 +1252,9 @@
       <c r="H2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1">
@@ -1618,5 +1624,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>